--- a/excel/dosyalar/reports_mekmer_strips.xlsx
+++ b/excel/dosyalar/reports_mekmer_strips.xlsx
@@ -405,7 +405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="15" defaultRowHeight="14.4"/>
   <cols>
     <col width="15" customWidth="1" style="1" min="4" max="4"/>
@@ -420,45 +420,70 @@
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
+          <t>İrsaliye No</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
           <t>Tedarikçi Adı</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Ocak Adı</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Strip Adı</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Fatura No</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Strip (M2)</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Strip ($)</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Strip (₺)</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Strip Toplam (₺)</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Strip Toplam ($)</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Kur (₺)</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>En</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>Boy</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Kalınlık</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>Adet</t>
         </is>
@@ -467,41 +492,2073 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>20-08-2024</t>
+          <t>03-01-2026</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Cyl Mermer</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>FABER</t>
+          <t>NUOVA</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Classic Vein Cut</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="n">
+          <t>ALIMOGLU</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>ÇİMENTO</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>NUO202600003</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>20.93</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>236.36</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>4947.01</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>115.16</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>42.96</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O2" s="4" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>03-01-2026</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>ALIMOGLU</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>ÇİMENTO</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>NUO202600003</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>236.36</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>4869.02</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>113.34</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>42.96</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>03-01-2026</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>ALIMOGLU</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>ÇİMENTO</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>NUO202600003</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>236.36</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>3895.21</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>90.67</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>42.96</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>03-01-2026</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>DEMİRELLER</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>SILVER</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>NUO202600003</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>236.36</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>3895.21</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>90.67</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>42.96</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>03-01-2026</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>ALIMOGLU</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>ÇİMENTO</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>NUO202600003</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>55.72</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>236.36</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>13169.98</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>306.58</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>42.96</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>03-01-2026</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>DEMİRELLER</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>SILVER</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>NUO202600003</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>37.15</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>236.36</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>8780.77</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>204.39</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>42.96</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O7" s="4" t="n">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>03-01-2026</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>DEMİRELLER</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>SILVER</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>NUO202600003</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>62.73</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>225.62</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>14153.14</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>329.46</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>42.96</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>121</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>03-01-2026</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>DEMİRELLER</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>SILVER</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>NUO202600003</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>225.62</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>1509.4</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>35.13</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>42.96</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O9" s="4" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>03-01-2026</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>DEMİRELLER</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>SILVER</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>NUO202600003</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>13.87</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>225.62</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>3129.35</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>72.84</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>42.96</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O10" s="4" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>05-01-2026</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>ALIMOGLU</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>ÇİMENTO</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>NUO202600003</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>44.65</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>257.85</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>11513</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>267.5</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O11" s="4" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>05-01-2026</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>ALIMOGLU</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>ÇİMENTO</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>NUO202600003</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>236.36</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>3895.21</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O12" s="4" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>05-01-2026</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>DEMİRELLER</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>SILVER</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>NUO202600003</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>236.36</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>3895.21</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O13" s="4" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>05-01-2026</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>ALIMOGLU</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>ÇİMENTO</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>NUO202600003</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>32.96</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>236.36</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>7790.43</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O14" s="4" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>05-01-2026</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>ALIMOGLU</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>ÇİMENTO</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>NUO202600003</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>236.36</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>17561.55</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>408.03</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="N15" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O15" s="4" t="n">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>05-01-2026</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>DEMİRELLER</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>SILVER</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>NUO202600003</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>236.36</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>8778.41</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>203.96</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>06-01-2026</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>ALIMOGLU</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>ÇİMENTO</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>NUO202600003</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>78.14</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>236.36</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>18469.17</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>429.12</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O17" s="4" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>06-01-2026</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>ALIMOGLU</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>ÇİMENTO</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>NUO202600003</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>236.36</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>4869.02</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>113.13</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="N18" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O18" s="4" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>06-01-2026</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>DEMİRELLER</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>SILVER</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>NUO202600003</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>236.36</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>3895.21</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="N19" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O19" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>06-01-2026</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>ALIMOGLU</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>ÇİMENTO</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>NUO202600003</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>236.36</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>8778.41</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>203.96</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="N20" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O20" s="4" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>06-01-2026</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>DEMİRELLER</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>SILVER</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>NUO202600003</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>78.14</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>236.36</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>18469.17</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>429.12</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O21" s="4" t="n">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>07-01-2026</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>ALIMOGLU</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>ÇİMENTO</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>NUO202600003</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>22.28</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>257.5</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>5737.1</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>133.27</v>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>43.05</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="M22" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="N22" s="4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O22" s="4" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>07-01-2026</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>ALIMOGLU</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>ÇİMENTO</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>NUO202600003</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>257.85</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>3607.32</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>83.79000000000001</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>43.05</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="N23" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O23" s="4" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>07-01-2026</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>ALIMOGLU</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>ÇİMENTO</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>NUO202600003</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>47.44</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>257.85</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>12232.4</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>284.14</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>43.05</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="N24" s="4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O24" s="4" t="n">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>10-01-2026</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>ALIMOGLU</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>ÇİMENTO</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr"/>
+      <c r="G25" s="4" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="4" t="n">
+        <v>43.06</v>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="M25" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="N25" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O25" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>10-01-2026</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>ALIMOGLU</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>ÇİMENTO</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="4" t="n">
+        <v>43.06</v>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="M26" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="N26" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O26" s="4" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>10-01-2026</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>DEMİRELLER</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>SILVER</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>43.06</v>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="M27" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="N27" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O27" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>10-01-2026</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>ALIMOGLU</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>ÇİMENTO</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr"/>
+      <c r="G28" s="4" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="4" t="n">
+        <v>43.06</v>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="M28" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="N28" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O28" s="4" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>10-01-2026</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>DEMİRELLER</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>SILVER</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr"/>
+      <c r="G29" s="4" t="n">
+        <v>72.56</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="4" t="n">
+        <v>43.06</v>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="M29" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="N29" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O29" s="4" t="n">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>10-01-2026</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>ALIMOGLU</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>ÇİMENTO</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr"/>
+      <c r="G30" s="4" t="n">
+        <v>29.44</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>43.06</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="M30" s="4" t="n">
+        <v>123</v>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O30" s="4" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>12-01-2026</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>ALIMOGLU</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>ÇİMENTO</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr"/>
+      <c r="G31" s="4" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="4" t="n">
+        <v>43.14</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="M31" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="N31" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O31" s="4" t="n">
         <v>125</v>
       </c>
-      <c r="F2" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>1500</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>125</v>
-      </c>
-      <c r="J2" s="4" t="n">
-        <v>80</v>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>12-01-2026</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>ALIMOGLU</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Bilinmiyor</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr"/>
+      <c r="G32" s="4" t="n">
+        <v>55.81</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>43.14</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="M32" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="N32" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O32" s="4" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>12-01-2026</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>ALIMOGLU</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>ÇİMENTO</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr"/>
+      <c r="G33" s="4" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="4" t="n">
+        <v>43.14</v>
+      </c>
+      <c r="L33" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="M33" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="N33" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O33" s="4" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>12-01-2026</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>DEMİRELLER</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>SILVER</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr"/>
+      <c r="G34" s="4" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="4" t="n">
+        <v>43.14</v>
+      </c>
+      <c r="L34" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="M34" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="N34" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O34" s="4" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>12-01-2026</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>ALIMOGLU</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>ÇİMENTO</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr"/>
+      <c r="G35" s="4" t="n">
+        <v>71.29000000000001</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="4" t="n">
+        <v>43.14</v>
+      </c>
+      <c r="L35" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="M35" s="4" t="n">
+        <v>123</v>
+      </c>
+      <c r="N35" s="4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O35" s="4" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>12-01-2026</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>ALIMOGLU</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>ÇİMENTO</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr"/>
+      <c r="G36" s="4" t="n">
+        <v>32.54</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>43.14</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="M36" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="N36" s="4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O36" s="4" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>12-01-2026</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>NUOVA</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>DEMİRELLER</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>SILVER</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr"/>
+      <c r="G37" s="4" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="4" t="n">
+        <v>43.14</v>
+      </c>
+      <c r="L37" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="M37" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="N37" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O37" s="4" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
